--- a/Dashboards/data/Data final/empleo/salarios/salarios_series.xlsx
+++ b/Dashboards/data/Data final/empleo/salarios/salarios_series.xlsx
@@ -910,7 +910,7 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>439.2515</v>
+        <v>438.2275</v>
       </c>
     </row>
     <row r="38">
@@ -936,7 +936,7 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>462.7593</v>
+        <v>471.3531</v>
       </c>
     </row>
     <row r="40">
@@ -962,7 +962,7 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>462.3622</v>
+        <v>460.6127</v>
       </c>
     </row>
     <row r="42">
@@ -988,7 +988,7 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>463.8172</v>
+        <v>447.2546</v>
       </c>
     </row>
     <row r="44">
@@ -1014,7 +1014,7 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>482.9985</v>
+        <v>514.4290999999999</v>
       </c>
     </row>
   </sheetData>
